--- a/public/research/cross-domain-matrix.xlsx
+++ b/public/research/cross-domain-matrix.xlsx
@@ -8,6 +8,7 @@
     <sheet name="Color Semantics" sheetId="3" r:id="rId3"/>
     <sheet name="Feature Priority" sheetId="4" r:id="rId4"/>
     <sheet name="UX Patterns" sheetId="5" r:id="rId5"/>
+    <sheet name="MOAT Features" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -1312,7 +1313,7 @@
         <v>All</v>
       </c>
       <c r="F4" t="str">
-        <v>Planned</v>
+        <v>Implemented</v>
       </c>
     </row>
     <row r="5">
@@ -1332,7 +1333,7 @@
         <v>B+C</v>
       </c>
       <c r="F5" t="str">
-        <v>Planned</v>
+        <v>Implemented</v>
       </c>
     </row>
     <row r="6">
@@ -1352,7 +1353,7 @@
         <v>A</v>
       </c>
       <c r="F6" t="str">
-        <v>Planned</v>
+        <v>Implemented</v>
       </c>
     </row>
     <row r="7">
@@ -1372,7 +1373,7 @@
         <v>A→B</v>
       </c>
       <c r="F7" t="str">
-        <v>Planned</v>
+        <v>Implemented</v>
       </c>
     </row>
     <row r="8">
@@ -1460,4 +1461,275 @@
     <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F13"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Feature</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Domain</v>
+      </c>
+      <c r="C1" t="str">
+        <v>MOAT Type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Switching Cost</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Marketing Health Score</v>
+      </c>
+      <c r="B2" t="str">
+        <v>HealthTech</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Data + Habit</v>
+      </c>
+      <c r="D2" t="str">
+        <v>High — score history</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Tier 1</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Implemented</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Confidence Indicators</v>
+      </c>
+      <c r="B3" t="str">
+        <v>FinTech</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Trust</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Medium — reliance</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Tier 1</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Implemented</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Achievement System</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Gaming</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Sunk Cost</v>
+      </c>
+      <c r="D4" t="str">
+        <v>High — earned badges</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Tier 1</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Implemented</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Weekly Pulse</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Content/Media</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Habit</v>
+      </c>
+      <c r="D5" t="str">
+        <v>High — routine</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Tier 1</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Implemented</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Social Proof</v>
+      </c>
+      <c r="B6" t="str">
+        <v>E-Commerce</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Trust</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Tier 1</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Implemented</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Contextual Help Glossary</v>
+      </c>
+      <c r="B7" t="str">
+        <v>EdTech</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Knowledge Lock-in</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Medium — learned here</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Tier 1</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Implemented</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AI Marketing Coach</v>
+      </c>
+      <c r="B8" t="str">
+        <v>AI/ML</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Data + Personalization</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Very High — knows you</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Tier 2</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Planned</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Plan Comparison</v>
+      </c>
+      <c r="B9" t="str">
+        <v>FinTech</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Data</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Medium — multiple plans</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Tier 2</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Planned</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Template Marketplace</v>
+      </c>
+      <c r="B10" t="str">
+        <v>SaaS/PLG</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Network Effect</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Very High — community</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Tier 2</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Planned</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Learning Path</v>
+      </c>
+      <c r="B11" t="str">
+        <v>EdTech</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Knowledge</v>
+      </c>
+      <c r="D11" t="str">
+        <v>High — progress lost</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Tier 2</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Planned</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>WhatsApp Community Bot</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Social</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Network + Habit</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Very High</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Tier 3</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Planned</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Benchmark Dashboard</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Data/Analytics</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Data Flywheel</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Maximum</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Tier 3</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Planned</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
+  </ignoredErrors>
+</worksheet>
 </file>